--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2020_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2020_coquimbo.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:12</t>
+    <t xml:space="preserve">2026-09-24 01:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -938,13 +938,13 @@
         <v>-0.9</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>-0.8</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>-0.1</v>
@@ -961,13 +961,13 @@
         <v>-0.51</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>-0.33</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>-0.18</v>
@@ -984,13 +984,13 @@
         <v>-0.71</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>-0.63</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>-0.08</v>
@@ -1004,19 +1004,19 @@
         <v>26</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.38</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>-0.32</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="22">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2020_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2020_coquimbo.xlsx
@@ -117,7 +117,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:02</t>
+    <t xml:space="preserve">2026-10-01 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2020_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2020_coquimbo.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:11</t>
+    <t xml:space="preserve">2026-10-05 19:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
